--- a/ig/Bac-à-sable-dan/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/Bac-à-sable-dan/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T10:24:30+00:00</t>
+    <t>2024-11-25T16:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
